--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_135_R14.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_135_R14.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>M. RUBSTAVICIUS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.952</v>
+        <v>1.8419</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1612</v>
+        <v>1.1116</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7908</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2541</v>
+        <v>1.5771</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-0.9423</v>
       </c>
       <c r="I2" t="n">
-        <v>1.044</v>
+        <v>2.5194</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1102</v>
+        <v>1.2949</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.7359</v>
+        <v>-0.7527</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6257</v>
+        <v>2.0476</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3644</v>
+        <v>0.2822</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0539</v>
+        <v>-0.1896</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4183</v>
+        <v>0.4718</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S2" t="n">
-        <v>1.002</v>
+        <v>0.6565</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2715</v>
+        <v>0.4404</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7306</v>
+        <v>0.2161</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. RUBSTAVICIUS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2522</v>
+        <v>1.3152</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5219</v>
+        <v>-1.2753</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7302999999999999</v>
+        <v>2.5905</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5771</v>
+        <v>1.75</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9423</v>
+        <v>1.3986</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5194</v>
+        <v>0.3513</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2949</v>
+        <v>-0.0585</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7527</v>
+        <v>0.3732</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0476</v>
+        <v>-0.4317</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2822</v>
+        <v>1.8085</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1896</v>
+        <v>1.0254</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4718</v>
+        <v>0.7831</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0668</v>
+        <v>0.5858</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1494</v>
+        <v>0.7316</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2161</v>
+        <v>-0.1458</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5361</v>
+        <v>-0.7886</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5361</v>
+        <v>-0.7886</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8315</v>
+        <v>1.1613</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.11</v>
+        <v>-0.1926</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9416</v>
+        <v>1.3539</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.6363</v>
+        <v>0.2541</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.2883</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.348</v>
+        <v>1.044</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.1708</v>
+        <v>-0.1102</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.5622</v>
+        <v>-0.7359</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3914</v>
+        <v>0.6257</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4655</v>
+        <v>0.3644</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7261</v>
+        <v>-0.0539</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0.4183</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0735</v>
+        <v>0.2113</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6844</v>
+        <v>-0.0824</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3891</v>
+        <v>0.2937</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9304</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6178</v>
+        <v>0.5194</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7038</v>
+        <v>-1.1533</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3216</v>
+        <v>1.6727</v>
       </c>
       <c r="G5" t="n">
-        <v>1.75</v>
+        <v>-2.6363</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3986</v>
+        <v>-2.2883</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3513</v>
+        <v>-0.348</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0585</v>
+        <v>-1.1708</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3732</v>
+        <v>-1.5622</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4317</v>
+        <v>0.3914</v>
       </c>
       <c r="M5" t="n">
-        <v>1.8085</v>
+        <v>-1.4655</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0254</v>
+        <v>-0.7261</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7831</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1116</v>
+        <v>1.7614</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3031</v>
+        <v>0.6411</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4147</v>
+        <v>1.1202</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7886</v>
+        <v>0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7886</v>
+        <v>0.5361</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.142</v>
+        <v>-0.2363</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3508</v>
+        <v>-2.9721</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2087</v>
+        <v>2.7358</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5283</v>
+        <v>-3.2942</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7924</v>
+        <v>2.8258</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.736</v>
+        <v>-6.1199</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.3713</v>
+        <v>-3.2728</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.4817</v>
+        <v>2.158</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1104</v>
+        <v>-5.4308</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1571</v>
+        <v>-0.0214</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6893</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8464</v>
+        <v>-0.6891</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6362</v>
+        <v>1.2562</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1982</v>
+        <v>0.4448</v>
       </c>
       <c r="U6" t="n">
-        <v>0.438</v>
+        <v>0.8114</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1418</v>
+        <v>2.0336</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>2.1754</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7478</v>
+        <v>-0.6806</v>
       </c>
       <c r="E7" t="n">
         <v>-2.1054</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3575</v>
+        <v>1.4247</v>
       </c>
       <c r="G7" t="n">
         <v>-0.7232</v>
@@ -1000,13 +1000,13 @@
         <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9577</v>
+        <v>-0.8905</v>
       </c>
       <c r="T7" t="n">
         <v>-0.7231</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2346</v>
+        <v>-0.1674</v>
       </c>
       <c r="V7" t="n">
         <v>1.8608</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4911</v>
+        <v>-1.6253</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.604</v>
+        <v>-3.0021</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1129</v>
+        <v>1.3768</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.9597</v>
+        <v>-1.5283</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.6988</v>
+        <v>-0.7924</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2609</v>
+        <v>-0.736</v>
       </c>
       <c r="J8" t="n">
-        <v>-6.5599</v>
+        <v>-1.3713</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.884</v>
+        <v>-1.4817</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.1104</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6002</v>
+        <v>-0.1571</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1852</v>
+        <v>0.6893</v>
       </c>
       <c r="O8" t="n">
-        <v>0.415</v>
+        <v>-0.8464</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q8" t="n">
+        <v>-2.3195</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.9278</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.1529</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.5469000000000001</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.3195</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.1491</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.8837</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.2653</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.0722</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5144</v>
+        <v>-1.8124</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.183</v>
+        <v>-3.0046</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6686</v>
+        <v>1.1922</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2942</v>
+        <v>-2.1895</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8258</v>
+        <v>-1.527</v>
       </c>
       <c r="I9" t="n">
-        <v>-6.1199</v>
+        <v>-0.6625</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.2728</v>
+        <v>-2.1287</v>
       </c>
       <c r="K9" t="n">
-        <v>2.158</v>
+        <v>-1.7338</v>
       </c>
       <c r="L9" t="n">
-        <v>-5.4308</v>
+        <v>-0.3949</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0214</v>
+        <v>-0.0608</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.2067</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6891</v>
+        <v>-0.2676</v>
       </c>
       <c r="P9" t="n">
         <v>-0.232</v>
@@ -1156,28 +1156,28 @@
         <v>2.0876</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.022</v>
+        <v>-0.3213</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7662</v>
+        <v>-0.1647</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7442</v>
+        <v>-0.1566</v>
       </c>
       <c r="V9" t="n">
-        <v>2.0336</v>
+        <v>0.9304</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1754</v>
+        <v>1.6083</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6284</v>
+        <v>-2.1167</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9504</v>
+        <v>-4.1623</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.678</v>
+        <v>2.0456</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3138</v>
+        <v>-5.9597</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1991</v>
+        <v>-5.6988</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1147</v>
+        <v>-0.2609</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5023</v>
+        <v>-6.5599</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0336</v>
+        <v>-5.884</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5359</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8116</v>
+        <v>0.6002</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2327</v>
+        <v>0.1852</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5788</v>
+        <v>0.415</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5465</v>
+        <v>1.5235</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4481</v>
+        <v>1.3254</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0984</v>
+        <v>0.1981</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8135</v>
+        <v>-2.5104</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5451</v>
+        <v>-1.8324</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2684</v>
+        <v>-0.678</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0611</v>
+        <v>-2.3138</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5295</v>
+        <v>-0.1991</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4684</v>
+        <v>-2.1147</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1395</v>
+        <v>-1.5023</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3228</v>
+        <v>0.0336</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4623</v>
+        <v>-1.5359</v>
       </c>
       <c r="M11" t="n">
-        <v>1.2006</v>
+        <v>-0.8116</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2067</v>
+        <v>-0.2327</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9939</v>
+        <v>-0.5788</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0532</v>
+        <v>-0.4285</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3778</v>
+        <v>-0.3301</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3246</v>
+        <v>-0.0984</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8375</v>
+        <v>-2.7635</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8617</v>
+        <v>-2.6631</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0242</v>
+        <v>-0.1004</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1895</v>
+        <v>0.0611</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.527</v>
+        <v>0.5295</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6625</v>
+        <v>-0.4684</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.1287</v>
+        <v>-1.1395</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.7338</v>
+        <v>0.3228</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3949</v>
+        <v>-1.4623</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0608</v>
+        <v>1.2006</v>
       </c>
       <c r="N12" t="n">
         <v>0.2067</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2676</v>
+        <v>0.9939</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.232</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3465</v>
+        <v>0.1032</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0218</v>
+        <v>0.2598</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3246</v>
+        <v>-0.1566</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9304</v>
+        <v>-1.0722</v>
       </c>
       <c r="W12" t="n">
-        <v>1.6083</v>
+        <v>0.5361</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9664</v>
+        <v>-4.8335</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4562</v>
+        <v>-2.1888</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5103</v>
+        <v>-2.6447</v>
       </c>
       <c r="G13" t="n">
         <v>-3.3691</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.239</v>
+        <v>-0.1061</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0474</v>
+        <v>0.3148</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2864</v>
+        <v>-0.4208</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2862</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.4876</v>
+        <v>-11.7409</v>
       </c>
       <c r="E14" t="n">
-        <v>-24.1873</v>
+        <v>-23.4404</v>
       </c>
       <c r="F14" t="n">
-        <v>11.6995</v>
+        <v>11.6994</v>
       </c>
       <c r="G14" t="n">
         <v>-18.3718</v>
@@ -1525,13 +1525,13 @@
         <v>-10.1464</v>
       </c>
       <c r="L14" t="n">
-        <v>-9.670999999999999</v>
+        <v>-9.670999999999998</v>
       </c>
       <c r="M14" t="n">
         <v>1.4455</v>
       </c>
       <c r="N14" t="n">
-        <v>1.227100000000001</v>
+        <v>1.2271</v>
       </c>
       <c r="O14" t="n">
         <v>0.2186000000000001</v>
@@ -1546,19 +1546,19 @@
         <v>12.7576</v>
       </c>
       <c r="S14" t="n">
-        <v>4.757500000000001</v>
+        <v>5.504400000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6575</v>
+        <v>3.4045</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>2.099900000000001</v>
       </c>
       <c r="V14" t="n">
         <v>2.2861</v>
       </c>
       <c r="W14" t="n">
-        <v>6.8896</v>
+        <v>6.889600000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-4.6035</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. LEAF</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.1225</v>
+        <v>6.3881</v>
       </c>
       <c r="E15" t="n">
-        <v>4.34</v>
+        <v>-0.7103</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7825</v>
+        <v>7.0984</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4325</v>
+        <v>3.4673</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0935</v>
+        <v>-0.4743</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3389</v>
+        <v>3.9416</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0344</v>
+        <v>-0.4463</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6281</v>
+        <v>-2.7148</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6625</v>
+        <v>2.2685</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3981</v>
+        <v>3.9136</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7217</v>
+        <v>2.2404</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6764</v>
+        <v>1.6732</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4639</v>
+        <v>2.3195</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4639</v>
+        <v>2.5515</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6178</v>
+        <v>-0.4709</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6973</v>
+        <v>-1.1042</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0795</v>
+        <v>0.6333</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>T. LEAF</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.168</v>
+        <v>5.6633</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8282</v>
+        <v>2.6886</v>
       </c>
       <c r="F16" t="n">
-        <v>6.9962</v>
+        <v>2.9747</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4673</v>
+        <v>2.4325</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4743</v>
+        <v>0.0935</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9416</v>
+        <v>2.3389</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4463</v>
+        <v>0.0344</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.7148</v>
+        <v>-0.6281</v>
       </c>
       <c r="L16" t="n">
-        <v>2.2685</v>
+        <v>0.6625</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9136</v>
+        <v>2.3981</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2404</v>
+        <v>0.7217</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6732</v>
+        <v>1.6764</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5515</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6909999999999999</v>
+        <v>1.1587</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2221</v>
+        <v>1.046</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5311</v>
+        <v>0.1127</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2557</v>
+        <v>5.2094</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3902</v>
+        <v>1.6261</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8655</v>
+        <v>3.5833</v>
       </c>
       <c r="G17" t="n">
         <v>7.0025</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.1411</v>
+        <v>-1.1874</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.5604</v>
+        <v>-1.3245</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5807</v>
+        <v>0.1371</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1418</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3555</v>
+        <v>4.5629</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2268</v>
+        <v>1.5807</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1286</v>
+        <v>2.9822</v>
       </c>
       <c r="G18" t="n">
         <v>3.3393</v>
@@ -1858,13 +1858,13 @@
         <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0561</v>
+        <v>0.1513</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0474</v>
+        <v>0.4013</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1035</v>
+        <v>-0.25</v>
       </c>
       <c r="V18" t="n">
         <v>1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2632</v>
+        <v>1.3069</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0977</v>
+        <v>-0.6508</v>
       </c>
       <c r="F19" t="n">
-        <v>0.361</v>
+        <v>1.9577</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2341</v>
+        <v>0.225</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2905</v>
+        <v>1.7239</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9436</v>
+        <v>-1.499</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3444</v>
+        <v>-0.5113</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3444</v>
+        <v>0.8773</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.3887</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8897</v>
+        <v>0.7363</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0539</v>
+        <v>0.8466</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9436</v>
+        <v>-0.1103</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8694</v>
+        <v>-0.3793</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9006</v>
+        <v>-0.5854</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0312</v>
+        <v>0.206</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1444</v>
+        <v>-0.3943</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.1829</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9615</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.09950000000000001</v>
+        <v>-0.0684</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4764</v>
+        <v>-0.6875</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5759</v>
+        <v>0.6191</v>
       </c>
       <c r="G20" t="n">
-        <v>0.225</v>
+        <v>2.2341</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7239</v>
+        <v>1.2905</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.499</v>
+        <v>0.9436</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5113</v>
+        <v>1.3444</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8773</v>
+        <v>1.3444</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3887</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7363</v>
+        <v>0.8897</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8466</v>
+        <v>-0.0539</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1103</v>
+        <v>0.9436</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8556</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5867</v>
+        <v>0.5377</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.411</v>
+        <v>0.3108</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1757</v>
+        <v>0.2269</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3943</v>
+        <v>-2.1444</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6778999999999999</v>
+        <v>-1.1829</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-0.9615</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CLARK III</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5259</v>
+        <v>-1.2135</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.215</v>
+        <v>-5.3396</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6891</v>
+        <v>4.1261</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9244</v>
+        <v>0.6754</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0745</v>
+        <v>0.0396</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8499</v>
+        <v>0.6357</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4123</v>
+        <v>-2.1087</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9509</v>
+        <v>-1.7506</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5386</v>
+        <v>-0.3581</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3367</v>
+        <v>2.7841</v>
       </c>
       <c r="N21" t="n">
-        <v>1.0254</v>
+        <v>1.7902</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3113</v>
+        <v>0.9939</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9278</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-2.5515</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7029</v>
+        <v>-0.639</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4832</v>
+        <v>-0.8213</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2196</v>
+        <v>0.1823</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8197</v>
+        <v>0.1418</v>
       </c>
       <c r="W21" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-0.8197</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>J. CLARK III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6245</v>
+        <v>-1.4029</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.9294</v>
+        <v>-3.4509</v>
       </c>
       <c r="F22" t="n">
-        <v>4.3049</v>
+        <v>2.048</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6754</v>
+        <v>0.9244</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0396</v>
+        <v>0.0745</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6357</v>
+        <v>0.8499</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.1087</v>
+        <v>-0.4123</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.7506</v>
+        <v>-0.9509</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3581</v>
+        <v>0.5386</v>
       </c>
       <c r="M22" t="n">
-        <v>2.7841</v>
+        <v>1.3367</v>
       </c>
       <c r="N22" t="n">
-        <v>1.7902</v>
+        <v>1.0254</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9939</v>
+        <v>0.3113</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3917</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.5515</v>
+        <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0499</v>
+        <v>-0.5799</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.411</v>
+        <v>-0.7191</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3611</v>
+        <v>0.1393</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1418</v>
+        <v>-0.8197</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7449</v>
+        <v>-1.8298</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6976</v>
+        <v>-4.5796</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9527</v>
+        <v>2.7498</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1665</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4187</v>
+        <v>0.4964</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3778</v>
+        <v>0.4957</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7964</v>
+        <v>0.0007</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8813</v>
+        <v>-2.1965</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.662</v>
+        <v>-0.4261</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2194</v>
+        <v>-1.7704</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7623</v>
@@ -2326,13 +2326,13 @@
         <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5983000000000001</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0351</v>
+        <v>0.2008</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5632</v>
+        <v>-0.1142</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1444</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>12.4878</v>
+        <v>16.4195</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.949300000000003</v>
+        <v>-9.949399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>22.437</v>
+        <v>26.3689</v>
       </c>
       <c r="G25" t="n">
         <v>18.3717</v>
@@ -2404,13 +2404,13 @@
         <v>13.9172</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.7575</v>
+        <v>-0.8259000000000003</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.0997</v>
+        <v>-2.0999</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.6576</v>
+        <v>1.2741</v>
       </c>
       <c r="V25" t="n">
         <v>-2.286199999999999</v>
